--- a/output/StructureDefinition-RNDSPrescricaoMedicamento.xlsx
+++ b/output/StructureDefinition-RNDSPrescricaoMedicamento.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7270" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7270" uniqueCount="1004">
   <si>
     <t>Property</t>
   </si>
@@ -2872,6 +2872,10 @@
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -22310,7 +22314,7 @@
         <v>81</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>101</v>
+        <v>834</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>81</v>
@@ -22319,7 +22323,7 @@
         <v>81</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -22330,10 +22334,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22359,14 +22363,14 @@
         <v>828</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>81</v>
@@ -22415,7 +22419,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22427,7 +22431,7 @@
         <v>81</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>101</v>
+        <v>834</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>81</v>
@@ -22436,7 +22440,7 @@
         <v>81</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
@@ -22447,10 +22451,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22473,13 +22477,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22530,7 +22534,7 @@
         <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22548,10 +22552,10 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
@@ -22562,10 +22566,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22677,10 +22681,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22794,10 +22798,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22913,10 +22917,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22939,16 +22943,16 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22998,7 +23002,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -23019,7 +23023,7 @@
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -23030,10 +23034,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23145,10 +23149,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23262,10 +23266,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23381,10 +23385,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23410,10 +23414,10 @@
         <v>828</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23464,7 +23468,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -23476,7 +23480,7 @@
         <v>81</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>101</v>
+        <v>834</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>81</v>
@@ -23485,7 +23489,7 @@
         <v>81</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>81</v>
@@ -23496,10 +23500,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23522,13 +23526,13 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23579,7 +23583,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23600,7 +23604,7 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
@@ -23611,10 +23615,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23637,13 +23641,13 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23694,7 +23698,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23715,7 +23719,7 @@
         <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
@@ -23726,10 +23730,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23755,16 +23759,16 @@
         <v>218</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -23813,7 +23817,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23831,10 +23835,10 @@
         <v>81</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -23845,10 +23849,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23960,10 +23964,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24077,10 +24081,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24106,13 +24110,13 @@
         <v>427</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -24162,7 +24166,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -24171,7 +24175,7 @@
         <v>89</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>101</v>
@@ -24183,21 +24187,21 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24223,20 +24227,20 @@
         <v>427</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q176" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="R176" t="s" s="2">
         <v>81</v>
@@ -24281,7 +24285,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -24290,7 +24294,7 @@
         <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>101</v>
@@ -24302,21 +24306,21 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24342,13 +24346,13 @@
         <v>679</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24398,7 +24402,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -24416,24 +24420,24 @@
         <v>81</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24459,10 +24463,10 @@
         <v>828</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -24511,7 +24515,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -24523,30 +24527,30 @@
         <v>81</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>101</v>
+        <v>834</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24658,10 +24662,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24775,10 +24779,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24804,16 +24808,16 @@
         <v>620</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>81</v>
@@ -24862,7 +24866,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24883,21 +24887,21 @@
         <v>81</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24923,20 +24927,20 @@
         <v>109</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q182" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="R182" t="s" s="2">
         <v>81</v>
@@ -24960,10 +24964,10 @@
         <v>179</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>81</v>
@@ -24981,7 +24985,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -25002,21 +25006,21 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25042,14 +25046,14 @@
         <v>162</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>81</v>
@@ -25098,7 +25102,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -25119,21 +25123,21 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25159,14 +25163,14 @@
         <v>103</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -25215,7 +25219,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -25224,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>101</v>
@@ -25236,21 +25240,21 @@
         <v>81</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25276,16 +25280,16 @@
         <v>109</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
@@ -25334,7 +25338,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -25355,21 +25359,21 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25392,16 +25396,16 @@
         <v>81</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -25451,7 +25455,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25469,10 +25473,10 @@
         <v>81</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>81</v>
@@ -25483,10 +25487,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25512,10 +25516,10 @@
         <v>226</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -25566,7 +25570,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25587,7 +25591,7 @@
         <v>81</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>467</v>
@@ -25598,10 +25602,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25624,13 +25628,13 @@
         <v>81</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -25681,7 +25685,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25699,10 +25703,10 @@
         <v>81</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>81</v>
@@ -25713,10 +25717,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25828,10 +25832,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25945,10 +25949,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26064,10 +26068,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26090,16 +26094,16 @@
         <v>81</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -26128,10 +26132,10 @@
         <v>260</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>81</v>
@@ -26149,7 +26153,7 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>89</v>
@@ -26167,24 +26171,24 @@
         <v>81</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26210,10 +26214,10 @@
         <v>186</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -26243,10 +26247,10 @@
         <v>260</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>81</v>
@@ -26264,7 +26268,7 @@
         <v>81</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -26282,24 +26286,24 @@
         <v>81</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26322,13 +26326,13 @@
         <v>81</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26379,7 +26383,7 @@
         <v>81</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -26394,13 +26398,13 @@
         <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>81</v>
@@ -26411,14 +26415,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -26437,16 +26441,16 @@
         <v>81</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26496,7 +26500,7 @@
         <v>81</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26517,7 +26521,7 @@
         <v>81</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>81</v>
@@ -26528,10 +26532,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26554,16 +26558,16 @@
         <v>81</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26613,7 +26617,7 @@
         <v>81</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26628,13 +26632,13 @@
         <v>101</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>81</v>
